--- a/business_forms/039_security_system_delivery_form--business_forms.xlsx
+++ b/business_forms/039_security_system_delivery_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>client_details</t>
+          <t>client_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>client_details</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Client Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter client name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +547,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>product_details</t>
+          <t>client_address</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Product Details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Client Address</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter client address</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter product name</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,110 +601,130 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>security_company_details</t>
+          <t>product_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>security_company_details</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter product description</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>delivery_method</t>
+          <t>delivery_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>delivery_method</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Delivery Date</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select delivery date</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>delivery_status</t>
+          <t>delivery_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>delivery_status</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Delivery Time</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select delivery time</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>delivery_date</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Security Type</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select security type</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>delivery_method</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Delivery Method</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select delivery method</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>security_personnel</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Security Personnel</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter status</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +768,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>delivery_notes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Delivery Notes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter delivery notes</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -758,10 +798,14 @@
           <t>Contact Email</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter contact email</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -781,10 +825,14 @@
           <t>Contact Phone</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter contact phone</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -804,10 +852,14 @@
           <t>Assigned User</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select assigned user</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -827,10 +879,14 @@
           <t>Assigned Department</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select assigned department</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -850,33 +906,41 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter notes</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter contact name</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +952,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>contact_phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Contact Phone 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter contact phone</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>security_system_details</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Security System Details</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter security system details</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Contact Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>delivery_method</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Delivery Method</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>delivery_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Delivery Status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>delivery_notes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Delivery Notes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>delivery_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>delivery_time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Delivery Time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_user</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Assigned User</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +1037,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>security_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>fire_alarm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Fire Alarm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>security_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>security_camera</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Security Camera</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>security_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>access_control</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Access Control</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_4',_'value':_'option4'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 4', 'value': 'option4'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_5',_'value':_'option5'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 5', 'value': 'option5'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>assigned_user_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_6',_'value':_'option6'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 6', 'value': 'option6'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1233,80 +1144,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_11',_'value':_'option11'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 11', 'value': 'option11'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>assigned_department_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_12',_'value':_'option12'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 12', 'value': 'option12'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>assigned_department_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_13',_'value':_'option13'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 13', 'value': 'option13'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>assigned_department_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'option_14',_'value':_'option14'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 14', 'value': 'option14'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>assigned_department_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'option_15',_'value':_'option15'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 15', 'value': 'option15'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
